--- a/artfynd/A 34609-2026 artfynd.xlsx
+++ b/artfynd/A 34609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007709</v>
       </c>
       <c r="B2" t="n">
-        <v>92946</v>
+        <v>92948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007782</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137007783</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137007713</v>
       </c>
       <c r="B5" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137007610</v>
       </c>
       <c r="B6" t="n">
-        <v>98222</v>
+        <v>98228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137007612</v>
       </c>
       <c r="B7" t="n">
-        <v>98222</v>
+        <v>98228</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137007613</v>
       </c>
       <c r="B8" t="n">
-        <v>98222</v>
+        <v>98228</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34609-2026 artfynd.xlsx
+++ b/artfynd/A 34609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007709</v>
       </c>
       <c r="B2" t="n">
-        <v>92948</v>
+        <v>92950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007782</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137007783</v>
       </c>
       <c r="B4" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137007713</v>
       </c>
       <c r="B5" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137007610</v>
       </c>
       <c r="B6" t="n">
-        <v>98228</v>
+        <v>98230</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137007612</v>
       </c>
       <c r="B7" t="n">
-        <v>98228</v>
+        <v>98230</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137007613</v>
       </c>
       <c r="B8" t="n">
-        <v>98228</v>
+        <v>98230</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34609-2026 artfynd.xlsx
+++ b/artfynd/A 34609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007709</v>
       </c>
       <c r="B2" t="n">
-        <v>92950</v>
+        <v>92951</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007782</v>
       </c>
       <c r="B3" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137007783</v>
       </c>
       <c r="B4" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137007713</v>
       </c>
       <c r="B5" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137007610</v>
       </c>
       <c r="B6" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137007612</v>
       </c>
       <c r="B7" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137007613</v>
       </c>
       <c r="B8" t="n">
-        <v>98230</v>
+        <v>98231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34609-2026 artfynd.xlsx
+++ b/artfynd/A 34609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007709</v>
       </c>
       <c r="B2" t="n">
-        <v>92951</v>
+        <v>92957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007782</v>
       </c>
       <c r="B3" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137007783</v>
       </c>
       <c r="B4" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137007610</v>
       </c>
       <c r="B6" t="n">
-        <v>98231</v>
+        <v>98237</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137007612</v>
       </c>
       <c r="B7" t="n">
-        <v>98231</v>
+        <v>98237</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137007613</v>
       </c>
       <c r="B8" t="n">
-        <v>98231</v>
+        <v>98237</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34609-2026 artfynd.xlsx
+++ b/artfynd/A 34609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007709</v>
       </c>
       <c r="B2" t="n">
-        <v>92957</v>
+        <v>92961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007782</v>
       </c>
       <c r="B3" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137007783</v>
       </c>
       <c r="B4" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137007713</v>
       </c>
       <c r="B5" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137007610</v>
       </c>
       <c r="B6" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137007612</v>
       </c>
       <c r="B7" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137007613</v>
       </c>
       <c r="B8" t="n">
-        <v>98237</v>
+        <v>98241</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34609-2026 artfynd.xlsx
+++ b/artfynd/A 34609-2026 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>137007610</v>
       </c>
       <c r="B6" t="n">
-        <v>98241</v>
+        <v>98243</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137007612</v>
       </c>
       <c r="B7" t="n">
-        <v>98241</v>
+        <v>98243</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137007613</v>
       </c>
       <c r="B8" t="n">
-        <v>98241</v>
+        <v>98243</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34609-2026 artfynd.xlsx
+++ b/artfynd/A 34609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007709</v>
       </c>
       <c r="B2" t="n">
-        <v>92961</v>
+        <v>92963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007782</v>
       </c>
       <c r="B3" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137007783</v>
       </c>
       <c r="B4" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137007713</v>
       </c>
       <c r="B5" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137007610</v>
       </c>
       <c r="B6" t="n">
-        <v>98243</v>
+        <v>98245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137007612</v>
       </c>
       <c r="B7" t="n">
-        <v>98243</v>
+        <v>98245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137007613</v>
       </c>
       <c r="B8" t="n">
-        <v>98243</v>
+        <v>98245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34609-2026 artfynd.xlsx
+++ b/artfynd/A 34609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007709</v>
       </c>
       <c r="B2" t="n">
-        <v>92963</v>
+        <v>92976</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007782</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137007783</v>
       </c>
       <c r="B4" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137007713</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137007610</v>
       </c>
       <c r="B6" t="n">
-        <v>98245</v>
+        <v>98258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137007612</v>
       </c>
       <c r="B7" t="n">
-        <v>98245</v>
+        <v>98258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137007613</v>
       </c>
       <c r="B8" t="n">
-        <v>98245</v>
+        <v>98258</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34609-2026 artfynd.xlsx
+++ b/artfynd/A 34609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007709</v>
       </c>
       <c r="B2" t="n">
-        <v>92976</v>
+        <v>92978</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007782</v>
       </c>
       <c r="B3" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137007783</v>
       </c>
       <c r="B4" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137007713</v>
       </c>
       <c r="B5" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137007610</v>
       </c>
       <c r="B6" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137007612</v>
       </c>
       <c r="B7" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137007613</v>
       </c>
       <c r="B8" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34609-2026 artfynd.xlsx
+++ b/artfynd/A 34609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007709</v>
       </c>
       <c r="B2" t="n">
-        <v>92978</v>
+        <v>92981</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007782</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137007783</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137007610</v>
       </c>
       <c r="B6" t="n">
-        <v>98260</v>
+        <v>98263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137007612</v>
       </c>
       <c r="B7" t="n">
-        <v>98260</v>
+        <v>98263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137007613</v>
       </c>
       <c r="B8" t="n">
-        <v>98260</v>
+        <v>98263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34609-2026 artfynd.xlsx
+++ b/artfynd/A 34609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007709</v>
       </c>
       <c r="B2" t="n">
-        <v>92981</v>
+        <v>92991</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007782</v>
       </c>
       <c r="B3" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137007783</v>
       </c>
       <c r="B4" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137007713</v>
       </c>
       <c r="B5" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137007610</v>
       </c>
       <c r="B6" t="n">
-        <v>98263</v>
+        <v>98273</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137007612</v>
       </c>
       <c r="B7" t="n">
-        <v>98263</v>
+        <v>98273</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137007613</v>
       </c>
       <c r="B8" t="n">
-        <v>98263</v>
+        <v>98273</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34609-2026 artfynd.xlsx
+++ b/artfynd/A 34609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007709</v>
       </c>
       <c r="B2" t="n">
-        <v>92991</v>
+        <v>92992</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007782</v>
       </c>
       <c r="B3" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137007783</v>
       </c>
       <c r="B4" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137007610</v>
       </c>
       <c r="B6" t="n">
-        <v>98273</v>
+        <v>98274</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137007612</v>
       </c>
       <c r="B7" t="n">
-        <v>98273</v>
+        <v>98274</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137007613</v>
       </c>
       <c r="B8" t="n">
-        <v>98273</v>
+        <v>98274</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34609-2026 artfynd.xlsx
+++ b/artfynd/A 34609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007709</v>
       </c>
       <c r="B2" t="n">
-        <v>92992</v>
+        <v>92995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007782</v>
       </c>
       <c r="B3" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137007783</v>
       </c>
       <c r="B4" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137007713</v>
       </c>
       <c r="B5" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137007610</v>
       </c>
       <c r="B6" t="n">
-        <v>98274</v>
+        <v>98279</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137007612</v>
       </c>
       <c r="B7" t="n">
-        <v>98274</v>
+        <v>98279</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137007613</v>
       </c>
       <c r="B8" t="n">
-        <v>98274</v>
+        <v>98279</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34609-2026 artfynd.xlsx
+++ b/artfynd/A 34609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007709</v>
       </c>
       <c r="B2" t="n">
-        <v>92995</v>
+        <v>92997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007782</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137007783</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137007610</v>
       </c>
       <c r="B6" t="n">
-        <v>98279</v>
+        <v>98281</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137007612</v>
       </c>
       <c r="B7" t="n">
-        <v>98279</v>
+        <v>98281</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137007613</v>
       </c>
       <c r="B8" t="n">
-        <v>98279</v>
+        <v>98281</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34609-2026 artfynd.xlsx
+++ b/artfynd/A 34609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007709</v>
       </c>
       <c r="B2" t="n">
-        <v>92997</v>
+        <v>93003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007782</v>
       </c>
       <c r="B3" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137007783</v>
       </c>
       <c r="B4" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137007713</v>
       </c>
       <c r="B5" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137007610</v>
       </c>
       <c r="B6" t="n">
-        <v>98281</v>
+        <v>98287</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137007612</v>
       </c>
       <c r="B7" t="n">
-        <v>98281</v>
+        <v>98287</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137007613</v>
       </c>
       <c r="B8" t="n">
-        <v>98281</v>
+        <v>98287</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34609-2026 artfynd.xlsx
+++ b/artfynd/A 34609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007709</v>
       </c>
       <c r="B2" t="n">
-        <v>93003</v>
+        <v>93015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007782</v>
       </c>
       <c r="B3" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137007783</v>
       </c>
       <c r="B4" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137007713</v>
       </c>
       <c r="B5" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137007610</v>
       </c>
       <c r="B6" t="n">
-        <v>98287</v>
+        <v>98299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137007612</v>
       </c>
       <c r="B7" t="n">
-        <v>98287</v>
+        <v>98299</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137007613</v>
       </c>
       <c r="B8" t="n">
-        <v>98287</v>
+        <v>98299</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34609-2026 artfynd.xlsx
+++ b/artfynd/A 34609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007709</v>
       </c>
       <c r="B2" t="n">
-        <v>93015</v>
+        <v>93016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007782</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137007783</v>
       </c>
       <c r="B4" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137007713</v>
       </c>
       <c r="B5" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137007610</v>
       </c>
       <c r="B6" t="n">
-        <v>98299</v>
+        <v>98300</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137007612</v>
       </c>
       <c r="B7" t="n">
-        <v>98299</v>
+        <v>98300</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137007613</v>
       </c>
       <c r="B8" t="n">
-        <v>98299</v>
+        <v>98300</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34609-2026 artfynd.xlsx
+++ b/artfynd/A 34609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007709</v>
       </c>
       <c r="B2" t="n">
-        <v>93016</v>
+        <v>93019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007782</v>
       </c>
       <c r="B3" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137007783</v>
       </c>
       <c r="B4" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137007713</v>
       </c>
       <c r="B5" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137007610</v>
       </c>
       <c r="B6" t="n">
-        <v>98300</v>
+        <v>98303</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137007612</v>
       </c>
       <c r="B7" t="n">
-        <v>98300</v>
+        <v>98303</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137007613</v>
       </c>
       <c r="B8" t="n">
-        <v>98300</v>
+        <v>98303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34609-2026 artfynd.xlsx
+++ b/artfynd/A 34609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007709</v>
       </c>
       <c r="B2" t="n">
-        <v>93019</v>
+        <v>93020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007782</v>
       </c>
       <c r="B3" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137007783</v>
       </c>
       <c r="B4" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137007713</v>
       </c>
       <c r="B5" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137007610</v>
       </c>
       <c r="B6" t="n">
-        <v>98303</v>
+        <v>98304</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137007612</v>
       </c>
       <c r="B7" t="n">
-        <v>98303</v>
+        <v>98304</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137007613</v>
       </c>
       <c r="B8" t="n">
-        <v>98303</v>
+        <v>98304</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34609-2026 artfynd.xlsx
+++ b/artfynd/A 34609-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007709</v>
       </c>
       <c r="B2" t="n">
-        <v>93020</v>
+        <v>93023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007782</v>
       </c>
       <c r="B3" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137007783</v>
       </c>
       <c r="B4" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137007713</v>
       </c>
       <c r="B5" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137007610</v>
       </c>
       <c r="B6" t="n">
-        <v>98304</v>
+        <v>98307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137007612</v>
       </c>
       <c r="B7" t="n">
-        <v>98304</v>
+        <v>98307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>137007613</v>
       </c>
       <c r="B8" t="n">
-        <v>98304</v>
+        <v>98307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
